--- a/songlist.xlsx
+++ b/songlist.xlsx
@@ -6,7 +6,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Songs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Songs'!$A$1:$J$1924</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Songs'!$A$1:$J$1927</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -10388,7 +10388,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>k3</t>
+          <t>Just Dance Kids 2014</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -13763,7 +13763,7 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>zh3</t>
+          <t>Just Dance 2017 (Chinese Version)</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
@@ -13808,7 +13808,7 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>zh3</t>
+          <t>Just Dance 2017 (Chinese Version)</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>abba</t>
+          <t>ABBA: You Can Dance</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
@@ -15343,7 +15343,7 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>abba</t>
+          <t>ABBA: You Can Dance</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>jduc</t>
+          <t>Just Dance Unlimited (Chinese Version)</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
@@ -16298,7 +16298,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>abba</t>
+          <t>ABBA: You Can Dance</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
@@ -16343,7 +16343,7 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>abba</t>
+          <t>ABBA: You Can Dance</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
@@ -17738,7 +17738,7 @@
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>abba</t>
+          <t>ABBA: You Can Dance</t>
         </is>
       </c>
       <c r="G489" t="inlineStr">
@@ -17783,7 +17783,7 @@
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>abba</t>
+          <t>ABBA: You Can Dance</t>
         </is>
       </c>
       <c r="G490" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>k1</t>
+          <t>Just Dance Kids</t>
         </is>
       </c>
       <c r="G492" t="inlineStr">
@@ -17918,7 +17918,7 @@
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>k1</t>
+          <t>Just Dance Kids</t>
         </is>
       </c>
       <c r="G493" t="inlineStr">
@@ -19023,7 +19023,7 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>abba</t>
+          <t>ABBA: You Can Dance</t>
         </is>
       </c>
       <c r="G518" t="inlineStr">
@@ -19588,7 +19588,7 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>abba</t>
+          <t>ABBA: You Can Dance</t>
         </is>
       </c>
       <c r="G531" t="inlineStr">
@@ -21183,7 +21183,7 @@
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>abba</t>
+          <t>ABBA: You Can Dance</t>
         </is>
       </c>
       <c r="G567" t="inlineStr">
@@ -21583,7 +21583,7 @@
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>abba</t>
+          <t>ABBA: You Can Dance</t>
         </is>
       </c>
       <c r="G576" t="inlineStr">
@@ -21628,7 +21628,7 @@
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>abba</t>
+          <t>ABBA: You Can Dance</t>
         </is>
       </c>
       <c r="G577" t="inlineStr">
@@ -21763,7 +21763,7 @@
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>abba</t>
+          <t>ABBA: You Can Dance</t>
         </is>
       </c>
       <c r="G580" t="inlineStr">
@@ -22873,7 +22873,7 @@
       </c>
       <c r="J605" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Chill</t>
         </is>
       </c>
     </row>
@@ -23523,7 +23523,7 @@
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>now</t>
+          <t>Just Dance Now</t>
         </is>
       </c>
       <c r="G620" t="inlineStr">
@@ -25463,7 +25463,7 @@
       </c>
       <c r="I663" t="inlineStr">
         <is>
-          <t>Mediun</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J663" t="inlineStr">
@@ -25693,7 +25693,7 @@
       </c>
       <c r="J669" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Chill</t>
         </is>
       </c>
     </row>
@@ -30993,11 +30993,6 @@
           <t>Just Vibes</t>
         </is>
       </c>
-      <c r="C869" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="D869" t="inlineStr">
         <is>
           <t>Just Dance 2018</t>
@@ -31015,10 +31010,8 @@
           <t>Just Vibes</t>
         </is>
       </c>
-      <c r="C870" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+      <c r="C870" t="n">
+        <v>2017</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -31037,10 +31030,8 @@
           <t>Just Vibes</t>
         </is>
       </c>
-      <c r="C871" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+      <c r="C871" t="n">
+        <v>2011</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -31059,11 +31050,6 @@
           <t>Just Vibes</t>
         </is>
       </c>
-      <c r="C872" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="D872" t="inlineStr">
         <is>
           <t>Just Dance 2018</t>
@@ -31081,11 +31067,6 @@
           <t>Just Vibes</t>
         </is>
       </c>
-      <c r="C873" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="D873" t="inlineStr">
         <is>
           <t>Just Dance 2018</t>
@@ -31173,7 +31154,7 @@
       </c>
       <c r="J876" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Chill</t>
         </is>
       </c>
     </row>
@@ -31703,7 +31684,7 @@
       </c>
       <c r="J895" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Chill</t>
         </is>
       </c>
     </row>
@@ -31813,7 +31794,7 @@
       </c>
       <c r="J899" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Chill</t>
         </is>
       </c>
     </row>
@@ -32133,7 +32114,7 @@
       </c>
       <c r="J910" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Chill</t>
         </is>
       </c>
     </row>
@@ -33108,7 +33089,7 @@
       </c>
       <c r="J946" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Chill</t>
         </is>
       </c>
     </row>
@@ -33673,7 +33654,7 @@
       </c>
       <c r="J966" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Chill</t>
         </is>
       </c>
     </row>
@@ -34838,10 +34819,8 @@
           <t>Idina Menzel &amp; AURORA (Disney’s Frozen 2)</t>
         </is>
       </c>
-      <c r="C1011" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+      <c r="C1011" t="n">
+        <v>2019</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -35810,7 +35789,7 @@
       </c>
       <c r="J1047" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Chill</t>
         </is>
       </c>
     </row>
@@ -36115,7 +36094,7 @@
       </c>
       <c r="J1058" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Chill</t>
         </is>
       </c>
     </row>
@@ -36925,7 +36904,7 @@
       </c>
       <c r="J1088" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Chill</t>
         </is>
       </c>
     </row>
@@ -37240,7 +37219,7 @@
       </c>
       <c r="J1099" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Chill</t>
         </is>
       </c>
     </row>
@@ -37325,7 +37304,7 @@
       </c>
       <c r="J1102" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Chill</t>
         </is>
       </c>
     </row>
@@ -37385,7 +37364,7 @@
       </c>
       <c r="J1104" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Chill</t>
         </is>
       </c>
     </row>
@@ -37445,7 +37424,7 @@
       </c>
       <c r="J1106" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Chill</t>
         </is>
       </c>
     </row>
@@ -38520,7 +38499,7 @@
       </c>
       <c r="J1145" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Chill</t>
         </is>
       </c>
     </row>
@@ -42035,7 +42014,7 @@
       </c>
       <c r="E1249" t="inlineStr">
         <is>
-          <t>now</t>
+          <t>Just Dance Now</t>
         </is>
       </c>
       <c r="G1249" t="inlineStr">
@@ -43155,7 +43134,7 @@
       </c>
       <c r="E1281" t="inlineStr">
         <is>
-          <t>k3</t>
+          <t>Just Dance Kids 2014</t>
         </is>
       </c>
       <c r="G1281" t="inlineStr">
@@ -43190,7 +43169,7 @@
       </c>
       <c r="E1282" t="inlineStr">
         <is>
-          <t>k3</t>
+          <t>Just Dance Kids 2014</t>
         </is>
       </c>
       <c r="G1282" t="inlineStr">
@@ -43225,7 +43204,7 @@
       </c>
       <c r="E1283" t="inlineStr">
         <is>
-          <t>k3</t>
+          <t>Just Dance Kids 2014</t>
         </is>
       </c>
       <c r="G1283" t="inlineStr">
@@ -43260,7 +43239,7 @@
       </c>
       <c r="E1284" t="inlineStr">
         <is>
-          <t>k3</t>
+          <t>Just Dance Kids 2014</t>
         </is>
       </c>
       <c r="G1284" t="inlineStr">
@@ -43295,7 +43274,7 @@
       </c>
       <c r="E1285" t="inlineStr">
         <is>
-          <t>k1</t>
+          <t>Just Dance Kids</t>
         </is>
       </c>
       <c r="G1285" t="inlineStr">
@@ -43330,7 +43309,7 @@
       </c>
       <c r="E1286" t="inlineStr">
         <is>
-          <t>k2</t>
+          <t>Just Dance Kids 2</t>
         </is>
       </c>
       <c r="G1286" t="inlineStr">
@@ -43365,7 +43344,7 @@
       </c>
       <c r="E1287" t="inlineStr">
         <is>
-          <t>k2</t>
+          <t>Just Dance Kids 2</t>
         </is>
       </c>
       <c r="G1287" t="inlineStr">
@@ -43400,7 +43379,7 @@
       </c>
       <c r="E1288" t="inlineStr">
         <is>
-          <t>k3</t>
+          <t>Just Dance Kids 2014</t>
         </is>
       </c>
       <c r="G1288" t="inlineStr">
@@ -43750,7 +43729,7 @@
       </c>
       <c r="E1298" t="inlineStr">
         <is>
-          <t>rowspan="2" Just Dance Unlimited Exclusive</t>
+          <t>Just Dance Unlimited Exclusive</t>
         </is>
       </c>
       <c r="G1298" t="inlineStr">
@@ -45825,7 +45804,7 @@
       </c>
       <c r="E1357" t="inlineStr">
         <is>
-          <t>Just Dance 2018|Ubisoft Club unlockable</t>
+          <t>Just Dance 2018</t>
         </is>
       </c>
       <c r="G1357" t="inlineStr">
@@ -45860,7 +45839,7 @@
       </c>
       <c r="E1358" t="inlineStr">
         <is>
-          <t>Just Dance 2018|Regional exclusive</t>
+          <t>Just Dance 2018</t>
         </is>
       </c>
       <c r="G1358" t="inlineStr">
@@ -46175,7 +46154,7 @@
       </c>
       <c r="E1367" t="inlineStr">
         <is>
-          <t>k2</t>
+          <t>Just Dance Kids 2</t>
         </is>
       </c>
       <c r="G1367" t="inlineStr">
@@ -46210,7 +46189,7 @@
       </c>
       <c r="E1368" t="inlineStr">
         <is>
-          <t>k3</t>
+          <t>Just Dance Kids 2014</t>
         </is>
       </c>
       <c r="G1368" t="inlineStr">
@@ -46245,7 +46224,7 @@
       </c>
       <c r="E1369" t="inlineStr">
         <is>
-          <t>k1</t>
+          <t>Just Dance Kids</t>
         </is>
       </c>
       <c r="G1369" t="inlineStr">
@@ -46315,7 +46294,7 @@
       </c>
       <c r="E1371" t="inlineStr">
         <is>
-          <t>k1</t>
+          <t>Just Dance Kids</t>
         </is>
       </c>
       <c r="G1371" t="inlineStr">
@@ -46420,7 +46399,7 @@
       </c>
       <c r="E1374" t="inlineStr">
         <is>
-          <t>k1</t>
+          <t>Just Dance Kids</t>
         </is>
       </c>
       <c r="G1374" t="inlineStr">
@@ -46455,7 +46434,7 @@
       </c>
       <c r="E1375" t="inlineStr">
         <is>
-          <t>k3</t>
+          <t>Just Dance Kids 2014</t>
         </is>
       </c>
       <c r="G1375" t="inlineStr">
@@ -47750,7 +47729,7 @@
       </c>
       <c r="E1412" t="inlineStr">
         <is>
-          <t>Just Dance 2019|Regional exclusive</t>
+          <t>Just Dance 2019</t>
         </is>
       </c>
       <c r="G1412" t="inlineStr">
@@ -49645,7 +49624,7 @@
       </c>
       <c r="E1466" t="inlineStr">
         <is>
-          <t>wiiu</t>
+          <t>Just Dance Wii U</t>
         </is>
       </c>
       <c r="G1466" t="inlineStr">
@@ -51605,7 +51584,7 @@
       </c>
       <c r="E1522" t="inlineStr">
         <is>
-          <t>2020c</t>
+          <t>Just Dance China</t>
         </is>
       </c>
       <c r="G1522" t="inlineStr">
@@ -55131,12 +55110,12 @@
       </c>
       <c r="I1656" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="J1656" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Intense</t>
         </is>
       </c>
     </row>
@@ -55853,12 +55832,12 @@
       </c>
       <c r="I1687" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="J1687" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Chill</t>
         </is>
       </c>
     </row>
@@ -55913,12 +55892,12 @@
       </c>
       <c r="I1689" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J1689" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Intense</t>
         </is>
       </c>
     </row>
@@ -56375,7 +56354,7 @@
       </c>
       <c r="I1709" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Hard</t>
         </is>
       </c>
     </row>
@@ -56427,7 +56406,7 @@
       </c>
       <c r="I1711" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Hardest</t>
         </is>
       </c>
     </row>
@@ -56655,7 +56634,7 @@
       </c>
       <c r="I1721" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -56751,7 +56730,7 @@
       </c>
       <c r="I1725" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -56891,7 +56870,7 @@
       </c>
       <c r="I1731" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Hardest</t>
         </is>
       </c>
     </row>
@@ -57141,7 +57120,7 @@
       </c>
       <c r="I1742" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Hard</t>
         </is>
       </c>
     </row>
@@ -57215,7 +57194,7 @@
       </c>
       <c r="I1745" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Hard</t>
         </is>
       </c>
     </row>
@@ -57289,7 +57268,7 @@
       </c>
       <c r="I1748" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Hardest</t>
         </is>
       </c>
     </row>
@@ -57517,7 +57496,7 @@
       </c>
       <c r="I1758" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -57811,7 +57790,7 @@
       </c>
       <c r="I1771" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Hardest</t>
         </is>
       </c>
     </row>

--- a/songlist.xlsx
+++ b/songlist.xlsx
@@ -54156,7 +54156,7 @@
       </c>
       <c r="I1661" t="inlineStr">
         <is>
-          <t>Hardest</t>
+          <t>Extreme</t>
         </is>
       </c>
     </row>
@@ -54620,7 +54620,7 @@
       </c>
       <c r="I1681" t="inlineStr">
         <is>
-          <t>Hardest</t>
+          <t>Extreme</t>
         </is>
       </c>
     </row>
@@ -55018,7 +55018,7 @@
       </c>
       <c r="I1698" t="inlineStr">
         <is>
-          <t>Hardest</t>
+          <t>Extreme</t>
         </is>
       </c>
     </row>
@@ -55540,7 +55540,7 @@
       </c>
       <c r="I1721" t="inlineStr">
         <is>
-          <t>Hardest</t>
+          <t>Extreme</t>
         </is>
       </c>
     </row>
@@ -55992,7 +55992,7 @@
       </c>
       <c r="I1739" t="inlineStr">
         <is>
-          <t>Hardest</t>
+          <t>Extreme</t>
         </is>
       </c>
     </row>
@@ -56148,7 +56148,7 @@
       </c>
       <c r="I1745" t="inlineStr">
         <is>
-          <t>Hardest</t>
+          <t>Extreme</t>
         </is>
       </c>
     </row>
@@ -56304,7 +56304,7 @@
       </c>
       <c r="I1751" t="inlineStr">
         <is>
-          <t>Hardest</t>
+          <t>Extreme</t>
         </is>
       </c>
     </row>
@@ -56482,7 +56482,7 @@
       </c>
       <c r="I1758" t="inlineStr">
         <is>
-          <t>Hardest</t>
+          <t>Extreme</t>
         </is>
       </c>
     </row>
@@ -56578,7 +56578,7 @@
       </c>
       <c r="I1762" t="inlineStr">
         <is>
-          <t>Hardest</t>
+          <t>Extreme</t>
         </is>
       </c>
     </row>
@@ -56652,7 +56652,7 @@
       </c>
       <c r="I1765" t="inlineStr">
         <is>
-          <t>Hardest</t>
+          <t>Extreme</t>
         </is>
       </c>
     </row>
